--- a/data/trans_orig/P36B13_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B13_R-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17482</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36182</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>24315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>55807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390961</t>
+          <t>388717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>409661</t>
+          <t>409260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320227</t>
+          <t>320416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>335180</t>
+          <t>335253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>716383</t>
+          <t>716067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741058</t>
+          <t>741792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>46774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>42520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49653</t>
+          <t>50031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81868</t>
+          <t>81210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325957</t>
+          <t>326477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349026</t>
+          <t>349083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328186</t>
+          <t>326469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348185</t>
+          <t>347686</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>660372</t>
+          <t>661030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>692587</t>
+          <t>692209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42250</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70752</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55414</t>
+          <t>53502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86715</t>
+          <t>87641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446317</t>
+          <t>446955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474819</t>
+          <t>475187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141423</t>
+          <t>141519</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>157122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>595595</t>
+          <t>594669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>626896</t>
+          <t>628808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121924</t>
+          <t>120666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166174</t>
+          <t>166412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111262</t>
+          <t>111276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207970</t>
+          <t>207509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264177</t>
+          <t>266950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>979286</t>
+          <t>979048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1023536</t>
+          <t>1024794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711784</t>
+          <t>711770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>747852</t>
+          <t>747421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1704329</t>
+          <t>1701556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1760536</t>
+          <t>1760997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76283</t>
+          <t>75071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110824</t>
+          <t>111938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40397</t>
+          <t>40448</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>70766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124270</t>
+          <t>123268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170227</t>
+          <t>170486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504246</t>
+          <t>503132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538787</t>
+          <t>539999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>666156</t>
+          <t>665222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>695591</t>
+          <t>695540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1180831</t>
+          <t>1180572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1226788</t>
+          <t>1227790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53442</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81964</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52891</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85403</t>
+          <t>85772</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114930</t>
+          <t>115382</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>159515</t>
+          <t>159708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205181</t>
+          <t>204992</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233703</t>
+          <t>234111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>984800</t>
+          <t>984431</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1017312</t>
+          <t>1018307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1197833</t>
+          <t>1197640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1242418</t>
+          <t>1241966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>383408</t>
+          <t>381180</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>456218</t>
+          <t>457418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244609</t>
+          <t>245022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>308936</t>
+          <t>306987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>648716</t>
+          <t>642317</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>747410</t>
+          <t>746295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2908919</t>
+          <t>2907719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2981729</t>
+          <t>2983957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3199263</t>
+          <t>3201212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3263590</t>
+          <t>3263177</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6125926</t>
+          <t>6127041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6224620</t>
+          <t>6231019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36625</t>
+          <t>41606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>40460</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>55427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>480658</t>
+          <t>522121</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468587</t>
+          <t>509012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489284</t>
+          <t>532582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>434702</t>
+          <t>474873</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426403</t>
+          <t>467049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439398</t>
+          <t>479684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>915361</t>
+          <t>996995</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>903113</t>
+          <t>982028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>925204</t>
+          <t>1008705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445913</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445913</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445913</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951126</t>
+          <t>1037455</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951126</t>
+          <t>1037455</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951126</t>
+          <t>1037455</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,17 +3704,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62306</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426985</t>
+          <t>456236</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410296</t>
+          <t>438231</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436392</t>
+          <t>466514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>361661</t>
+          <t>401017</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350398</t>
+          <t>390630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369115</t>
+          <t>408328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>788645</t>
+          <t>857253</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>770781</t>
+          <t>838043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801789</t>
+          <t>871283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>421380</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833087</t>
+          <t>904592</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833087</t>
+          <t>904592</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833087</t>
+          <t>904592</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>271822</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>505370</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>275732</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39612</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>543873</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>393727</t>
+          <t>435144</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160179</t>
+          <t>419232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628562</t>
+          <t>446599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>163001</t>
+          <t>183153</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158902</t>
+          <t>178670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165518</t>
+          <t>186002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>556728</t>
+          <t>618297</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>288587</t>
+          <t>601180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>792848</t>
+          <t>629721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>665549</t>
+          <t>468947</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665549</t>
+          <t>468947</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>665549</t>
+          <t>468947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>832460</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>832460</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>832460</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115977</t>
+          <t>123159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50307</t>
+          <t>52429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>125592</t>
+          <t>137702</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86072</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156534</t>
+          <t>167861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4503,17 +4503,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>943859</t>
+          <t>1032377</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918842</t>
+          <t>1008684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>963853</t>
+          <t>1052988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>940803</t>
+          <t>820263</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>925128</t>
+          <t>806069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958838</t>
+          <t>830454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1884661</t>
+          <t>1852639</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1853719</t>
+          <t>1822480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924181</t>
+          <t>1875111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975435</t>
+          <t>858498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975435</t>
+          <t>858498</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975435</t>
+          <t>858498</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010253</t>
+          <t>1990341</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010253</t>
+          <t>1990341</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010253</t>
+          <t>1990341</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>39434</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20848</t>
+          <t>27567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>50143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72010</t>
+          <t>82415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>441598</t>
+          <t>527113</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>428583</t>
+          <t>509815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452766</t>
+          <t>538980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>817903</t>
+          <t>803249</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>807493</t>
+          <t>794089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>825719</t>
+          <t>811390</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1259501</t>
+          <t>1330362</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1241751</t>
+          <t>1313788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1272146</t>
+          <t>1346060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473614</t>
+          <t>566547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840147</t>
+          <t>829656</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840147</t>
+          <t>829656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840147</t>
+          <t>829656</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313761</t>
+          <t>1396203</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313761</t>
+          <t>1396203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313761</t>
+          <t>1396203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>53042</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>65740</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41728</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>88726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>215791</t>
+          <t>209456</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196288</t>
+          <t>191251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228451</t>
+          <t>224123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>726579</t>
+          <t>804256</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711051</t>
+          <t>789183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>737830</t>
+          <t>817231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>942370</t>
+          <t>1013713</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>919031</t>
+          <t>990727</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958015</t>
+          <t>1030534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759236</t>
+          <t>842225</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759236</t>
+          <t>842225</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759236</t>
+          <t>842225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999743</t>
+          <t>1079453</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999743</t>
+          <t>1079453</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999743</t>
+          <t>1079453</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>469296</t>
+          <t>255947</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228799</t>
+          <t>217759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1290304</t>
+          <t>296938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>123866</t>
+          <t>139281</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98381</t>
+          <t>118494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149959</t>
+          <t>165458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>593162</t>
+          <t>395228</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>346455</t>
+          <t>354089</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1400690</t>
+          <t>440369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2902618</t>
+          <t>3182447</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2081610</t>
+          <t>3141456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3143115</t>
+          <t>3220635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3444651</t>
+          <t>3486812</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3418558</t>
+          <t>3460635</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3470136</t>
+          <t>3507599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6347269</t>
+          <t>6669259</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5539741</t>
+          <t>6624118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6593976</t>
+          <t>6710398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371914</t>
+          <t>3438394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371914</t>
+          <t>3438394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371914</t>
+          <t>3438394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3568517</t>
+          <t>3626093</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3568517</t>
+          <t>3626093</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3568517</t>
+          <t>3626093</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6940431</t>
+          <t>7064487</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6940431</t>
+          <t>7064487</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6940431</t>
+          <t>7064487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
